--- a/docs/pmc_data_quality_audit_casebook_2026-08-26.xlsx
+++ b/docs/pmc_data_quality_audit_casebook_2026-08-26.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/pmc_v26_pdf_gt_20260816/documents/pmc13425563/middle.json
+          <t>$PMC_SOURCE_ROOT/documents/pmc13425563/middle.json
 page_idx=0
 /pdf_info/0/para_blocks/0/lines/0/spans/0/content</t>
         </is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/pmc_v26_pdf_gt_20260816/documents/pmc13215880/middle.json
+          <t>$PMC_SOURCE_ROOT/documents/pmc13215880/middle.json
 page_idx=6
 /pdf_info/6/para_blocks/9/lines/0/spans/0/content</t>
         </is>
@@ -731,7 +731,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/pmc_v26_pdf_gt_20260816/documents/pmc13424892/middle.json
+          <t>$PMC_SOURCE_ROOT/documents/pmc13424892/middle.json
 page_idx=0
 /pdf_info/0/para_blocks/0/lines/0/spans/0/content</t>
         </is>
@@ -791,7 +791,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/pmc_v26_pdf_gt_20260816/documents/pmc13252203/middle.json
+          <t>$PMC_SOURCE_ROOT/documents/pmc13252203/middle.json
 page_idx=17,18,19
 /pdf_info/{17,18,19}/para_blocks</t>
         </is>
@@ -853,7 +853,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/pmc_v26_pdf_gt_20260816/documents/pmc13435129/middle.json
+          <t>$PMC_SOURCE_ROOT/documents/pmc13435129/middle.json
 page_idx=33
 /pdf_info/33/para_blocks/9/blocks/0/lines/0/spans/0/image_path</t>
         </is>
@@ -913,7 +913,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/pmc_v26_pdf_gt_20260816/documents/pmc10933458/middle.json
+          <t>$PMC_SOURCE_ROOT/documents/pmc10933458/middle.json
 page_idx=20
 /pdf_info/20/para_blocks/2/blocks/0/lines/0/spans/0/html</t>
         </is>
@@ -973,7 +973,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/pmc_v26_pdf_gt_20260816/documents/pmc13424892/middle.json
+          <t>$PMC_SOURCE_ROOT/documents/pmc13424892/middle.json
 page_idx=0
 /pdf_info/0/para_blocks/0/lines/0/spans/0/content</t>
         </is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/pmc_v26_pdf_gt_20260816/documents/pmc13424070/middle.json
+          <t>$PMC_SOURCE_ROOT/documents/pmc13424070/middle.json
 page_idx=36: /pdf_info/36/para_blocks/10
 page_idx=37: /pdf_info/37/para_blocks/0</t>
         </is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/pmc_v26_pdf_gt_20260816/documents/pmc13426939/middle.json
+          <t>$PMC_SOURCE_ROOT/documents/pmc13426939/middle.json
 page_idx=25
 /pdf_info/25/para_blocks/3/lines/0/spans/0/content</t>
         </is>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/unlimited-ocr-posttrain/docs/pmc_data_quality_audit_casebook_2026-08-26.md</t>
+          <t>$POSTTRAIN_ROOT/docs/pmc_data_quality_audit_casebook_2026-08-26.md</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>完整证据链、限定和绝对路径见该文档。</t>
+          <t>完整证据链、限定和路径变量见该文档。</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/uocr_readoc_pmc_silver_mix_v1/train.jsonl</t>
+          <t>$LEGACY_MIX_ROOT/train.jsonl</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/uocr_readoc_pmc_silver_mix_v1/validation.jsonl</t>
+          <t>$LEGACY_MIX_ROOT/validation.jsonl</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/uocr_readoc_pmc_silver_mix_v1/test.jsonl</t>
+          <t>$LEGACY_MIX_ROOT/test.jsonl</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>/Users/guofengjiao/Documents/pmc_v26_pdf_gt_20260816/documents</t>
+          <t>$PMC_SOURCE_ROOT/documents</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
